--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230301_20230901.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230301_20230901.xlsx
@@ -1009,37 +1009,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60.97560975609756</v>
+        <v>59.34959349593496</v>
       </c>
       <c r="C14" t="n">
-        <v>37.39837398373984</v>
+        <v>39.83739837398374</v>
       </c>
       <c r="D14" t="n">
-        <v>73.45781099010526</v>
+        <v>86.87317153176926</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>INE463V01026</t>
+          <t>INE732I01013</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G14" t="n">
-        <v>-23.57723577235772</v>
+        <v>-19.51219512195122</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I14" t="n">
         <v>55</v>
       </c>
       <c r="J14" t="n">
-        <v>713.25</v>
+        <v>187</v>
       </c>
       <c r="K14" t="n">
         <v>13</v>
@@ -1053,37 +1053,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.34959349593496</v>
+        <v>60.97560975609756</v>
       </c>
       <c r="C15" t="n">
-        <v>39.83739837398374</v>
+        <v>37.39837398373984</v>
       </c>
       <c r="D15" t="n">
-        <v>86.87317153176926</v>
+        <v>73.45781099010526</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>INE732I01013</t>
+          <t>INE463V01026</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>-19.51219512195122</v>
+        <v>-23.57723577235772</v>
       </c>
       <c r="H15" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>55</v>
       </c>
       <c r="J15" t="n">
-        <v>187</v>
+        <v>713.25</v>
       </c>
       <c r="K15" t="n">
         <v>14</v>
